--- a/survey_templates/036_synthetic_food_ingredients_quiz--survey_templates.xlsx
+++ b/survey_templates/036_synthetic_food_ingredients_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,8 +658,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -687,12 +687,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2.1,_'name':_'i_don’t_know',_'description':_''}</t>
+          <t>i_don’t_know</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2.1, 'name': 'I don’t know', 'description': ''}</t>
+          <t>I don’t know</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.1',_'name':_'artificial_sweeteners_and_flavor_enhancers',_'description':_''}</t>
+          <t>artificial_sweeteners_and_flavor_enhancers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2.1.1', 'name': 'Artificial sweeteners and flavor enhancers', 'description': ''}</t>
+          <t>Artificial sweeteners and flavor enhancers</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.2',_'name':_'food_colorants',_'description':_''}</t>
+          <t>food_colorants</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '2.1.2', 'name': 'Food colorants', 'description': ''}</t>
+          <t>Food colorants</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.3',_'name':_'preservatives_and_acidulents',_'description':_''}</t>
+          <t>preservatives_and_acidulents</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '2.1.3', 'name': 'Preservatives and acidulents', 'description': ''}</t>
+          <t>Preservatives and acidulents</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.4',_'name':_'other',_'description':_''}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '2.1.4', 'name': 'Other', 'description': ''}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'name':_'monosodium_glutamate_(msg)',_'description':_''}</t>
+          <t>monosodium_glutamate_(msg)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'name': 'Monosodium glutamate (MSG)', 'description': ''}</t>
+          <t>Monosodium glutamate (MSG)</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3.2,_'name':_'aspartame',_'description':_''}</t>
+          <t>aspartame</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3.2, 'name': 'Aspartame', 'description': ''}</t>
+          <t>Aspartame</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3.3,_'name':_'carrageenan',_'description':_''}</t>
+          <t>carrageenan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3.3, 'name': 'Carrageenan', 'description': ''}</t>
+          <t>Carrageenan</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3.4,_'name':_'other',_'description':_''}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3.4, 'name': 'Other', 'description': ''}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
